--- a/Result/profitability/2420.xlsx
+++ b/Result/profitability/2420.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8975</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>44.14875</v>
+        <v>44.435</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8062499999999999</v>
+        <v>0.84375</v>
       </c>
       <c r="N3" t="n">
-        <v>42.315</v>
+        <v>42.53</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.52</v>
       </c>
       <c r="M4" t="n">
-        <v>0.75125</v>
+        <v>0.7825</v>
       </c>
       <c r="N4" t="n">
-        <v>39.43</v>
+        <v>40.2025</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.19</v>
       </c>
       <c r="M5" t="n">
-        <v>0.64875</v>
+        <v>0.71375</v>
       </c>
       <c r="N5" t="n">
-        <v>36.76375</v>
+        <v>37.325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0.575</v>
+        <v>0.61125</v>
       </c>
       <c r="N6" t="n">
-        <v>34.1225</v>
+        <v>34.89125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4425</v>
+        <v>0.45125</v>
       </c>
       <c r="N7" t="n">
-        <v>32.87</v>
+        <v>33.01000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>0.35375</v>
+        <v>0.38</v>
       </c>
       <c r="N8" t="n">
-        <v>30.6575</v>
+        <v>30.99</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2420</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>596</v>
+      </c>
+      <c r="D75" t="n">
+        <v>296</v>
+      </c>
+      <c r="E75" t="n">
+        <v>301</v>
+      </c>
+      <c r="F75" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>208</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>34.91%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>32</v>
+      </c>
+      <c r="J75" t="n">
+        <v>240</v>
+      </c>
+      <c r="K75" t="n">
+        <v>192</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>47.34375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.660000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05569514237855944</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.7027027027027026</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.490000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09775745699978233</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
